--- a/artfynd/A 13287-2022 artfynd.xlsx
+++ b/artfynd/A 13287-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13287-2022 artfynd.xlsx
+++ b/artfynd/A 13287-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16603179</v>
+        <v>56220840</v>
       </c>
       <c r="B2" t="n">
-        <v>85172</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>442</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697672.8421361031</v>
+        <v>697720</v>
       </c>
       <c r="R2" t="n">
-        <v>6682040.353796444</v>
+        <v>6681923</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,31 +749,21 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-09-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-09-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-10-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Troligen förstörd växtplats. Barrskogen där bullspindlingen tidigare växte slutavverkades omkring 2010. Känd sedan tidigare, se Gillis A. 24/10-06.</t>
+          <t>1 ex. i äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -779,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalhygge.</t>
+          <t>Äldre, örtrik barrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,50 +791,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16812338</v>
+        <v>69500884</v>
       </c>
       <c r="B3" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697638.6337126011</v>
+        <v>697720</v>
       </c>
       <c r="R3" t="n">
-        <v>6681990.716107</v>
+        <v>6681942</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,31 +861,21 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-09-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-10-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-09-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-10-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Troligen förstörd växtplats. Barrskogen där olivspindlingen tidigare växte slutavverkades omkring 2010. Känd sedan tidigare, se Gillis A. 24/10-06.</t>
+          <t>Ca. 20 ex. på en viltstig, i fuktig äldre barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
@@ -901,7 +885,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalhygge.</t>
+          <t>Äldre, örtrik barrskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -916,6 +900,1145 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>69500886</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87403</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>433</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>697677</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6681974</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 ex. i äldre, fuktig granskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>69500888</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87403</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>433</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>697738</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6681890</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 ex. i fuktig sluttning i äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>62076463</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87405</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>436</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blekspindling agg.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiostramineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>697690</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6682106</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 ex. i ca. 60-årig granskog.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>60-årig, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>62077774</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87233</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bullspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius corrosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>697673</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6682040</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 ex. under gran och tall i ca. 60-årig barrskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>60-årig, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>69506682</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87289</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>473</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Äggspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius meinhardii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>697691</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6682049</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ex. i körspår i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>75873426</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>697740</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6681901</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt i fuktig sluttning i äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>69510668</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>697734</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6681925</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 ex. i äldre, fuktig barrskog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>69510670</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>697639</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6681991</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 ex. i 40-årig barrskog.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>40-årig, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>75891303</v>
+      </c>
+      <c r="B12" t="n">
+        <v>89143</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>697733</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6681890</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca. 30 ex. i fuktig sluttning, i äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>75905854</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gruvhagaträsket 3,5 km SO om Nolsterby, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>697753</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6681906</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2006-10-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. i fuktig sluttning i äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13287-2022 artfynd.xlsx
+++ b/artfynd/A 13287-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220840</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69500884</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69500886</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69500888</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62076463</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62077774</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506682</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1575,6 +1615,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75873426</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1691,6 +1736,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510668</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1807,6 +1857,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510670</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1923,6 +1978,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75891303</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2039,8 +2099,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75905854</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>